--- a/esyluban/examples/dev/DataTables/test/test_constalias.xlsx
+++ b/esyluban/examples/dev/DataTables/test/test_constalias.xlsx
@@ -406,7 +406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1">
@@ -417,7 +417,7 @@
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t>full_name="test.TbTestConstAlias" &amp; value_type="test.TestConstAlias" &amp; read_schema_from_file="false" &amp; input="test/test_constalias.xlsx" &amp; output="test_tbtestconstalias"</t>
+          <t>full_name="test.TbTestConstAlias" &amp; input="test/test_constalias.xlsx"</t>
         </is>
       </c>
     </row>
@@ -527,20 +527,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
